--- a/samples/test_data_excel_json.xlsx
+++ b/samples/test_data_excel_json.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="R22d3b761469f42358f1a895fe2303a9c"/>
+    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="R88f502d9a5d14107a838f2bff11c3496"/>
   </x:sheets>
 </x:workbook>
 </file>
